--- a/diseases/d155/2000-2004.xlsx
+++ b/diseases/d155/2000-2004.xlsx
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -15877,7 +15877,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -19693,7 +19693,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24463,7 +24463,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -25417,7 +25417,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26371,7 +26371,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -27325,7 +27325,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28279,7 +28279,7 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -29233,7 +29233,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30187,7 +30187,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -31141,7 +31141,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -32095,7 +32095,7 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -33049,7 +33049,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34003,7 +34003,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -34957,7 +34957,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -35911,7 +35911,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -36865,7 +36865,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -37819,7 +37819,7 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -38773,7 +38773,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -39727,7 +39727,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -40681,7 +40681,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -41635,7 +41635,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -42589,7 +42589,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -43543,7 +43543,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -44497,7 +44497,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -45451,7 +45451,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -46405,7 +46405,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -47359,7 +47359,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -48313,7 +48313,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -49267,7 +49267,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -50221,7 +50221,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -51175,7 +51175,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -52129,7 +52129,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -53083,7 +53083,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -54037,7 +54037,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -54991,7 +54991,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -55945,7 +55945,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -56899,7 +56899,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -57853,7 +57853,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
